--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ZAARR-DTE\taylor-imops-lite\packages\backend\src\scripts\soverus\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4077CB6B-6D9F-4F7C-89A9-BA5B84A453B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCB3122-BD45-4F1E-81C6-48F121C81249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,9 +148,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L1_Lift Lobby</t>
   </si>
   <si>
-    <t>SOV 38ALT L1 Lift Lobby LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l1-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Corridor_o/s_War_Room</t>
   </si>
   <si>
-    <t>SOV 38ALT L4 Corridor o/s War Room LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-corridor-o-s-war-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Interlock</t>
   </si>
   <si>
-    <t>SOV 38ALT L4 Interlock LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-interlock-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -193,9 +184,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_Corridor</t>
   </si>
   <si>
-    <t>SOV 38ALT L5 Corridor LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-corridor-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -211,21 +199,12 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Side_Fencing</t>
   </si>
   <si>
-    <t>SOV 38ALT Side Fencing INTRUSION</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-intrusion -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
-    <t>SOV 38ALT Side Fencing SMOKING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-smoking -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
-    <t>SOV 38ALT Side Fencing FIRE</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-fire -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -238,9 +217,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Roof_Top</t>
   </si>
   <si>
-    <t>SOV 38ALT Roof Top LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-roof-top-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -253,9 +229,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Lift Lobby</t>
   </si>
   <si>
-    <t>SOV 38ALT L2 Lift Lobby LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -268,9 +241,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L3_Lift_Lobby</t>
   </si>
   <si>
-    <t>SOV_38ALT_L3_Lift_Lobby LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l3-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -283,9 +253,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Main_Lobby</t>
   </si>
   <si>
-    <t>SOV 38ALT L2 Main Lobby LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-main-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -298,9 +265,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Reception</t>
   </si>
   <si>
-    <t>SOV_38ALT_L2_Reception LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-reception-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -313,9 +277,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Road</t>
   </si>
   <si>
-    <t>SOV 38ALT Main Road LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-road-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -328,9 +289,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L6_Lift Lobby</t>
   </si>
   <si>
-    <t>SOV 38ALT L6 Lift Lobby LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l6-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -343,9 +301,6 @@
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_o/s_Cyber_Room</t>
   </si>
   <si>
-    <t>SOV 38ALT L5 o/s Cyber Room LOITERING</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-o-s-cyber-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -362,6 +317,51 @@
   </si>
   <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-gate-perimeter-intrusion -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L1 Lift Lobby VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L4 Corridor o/s War Room VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L4 Interlock VA  LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L5 Corridor VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Side Fencing VA INTRUSION</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Side Fencing  VA SMOKING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Side Fencing VA FIRE</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Roof Top VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L2 Lift Lobby VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV_38ALT_L3_Lift_Lobby VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L2 Main Lobby VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV_38ALT_L2_Reception VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Main Road VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L6 Lift Lobby VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L5 o/s Cyber Room VA LOITERING</t>
   </si>
 </sst>
 </file>
@@ -1076,13 +1076,13 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,13 +1093,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1114,13 +1114,13 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1131,13 +1131,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1152,13 +1152,13 @@
         <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1169,13 +1169,13 @@
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -1190,13 +1190,13 @@
         <v>2</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1204,37 +1204,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1245,13 +1245,13 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -1266,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1283,13 +1283,13 @@
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -1304,13 +1304,13 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1321,13 +1321,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -1342,13 +1342,13 @@
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1359,13 +1359,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -1380,13 +1380,13 @@
         <v>2</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1397,13 +1397,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1418,13 +1418,13 @@
         <v>2</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1435,13 +1435,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1456,13 +1456,13 @@
         <v>2</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1473,13 +1473,13 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -1494,13 +1494,13 @@
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1511,13 +1511,13 @@
         <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -1532,13 +1532,13 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1549,13 +1549,13 @@
         <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -1570,13 +1570,13 @@
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1587,13 +1587,13 @@
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -1608,13 +1608,13 @@
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1622,16 +1622,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
@@ -1646,13 +1646,13 @@
         <v>1</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ZAARR-DTE\taylor-imops-lite\packages\backend\src\scripts\soverus\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCB3122-BD45-4F1E-81C6-48F121C81249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8144BD96-94ED-40C3-AA2F-EA77F4E7718A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
   <si>
     <t>#</t>
   </si>
@@ -67,9 +67,6 @@
     <t>SOV_38ALT_L4_Lift_Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Lift_Lobby</t>
-  </si>
-  <si>
     <t>SOV 38ALT L4 LIFT LOBBY VA LOITERING</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>SOV_38ALT_L4_ ICC_1</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_%20ICC_1</t>
-  </si>
-  <si>
     <t>SOV 38ALT L4 ICC 1 VA CROWDING</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>SOV_38ALT_Main_Gate</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Gate</t>
-  </si>
-  <si>
     <t>SOV 38ALT Main Gate VA SMOKING</t>
   </si>
   <si>
@@ -130,9 +121,6 @@
     <t>SOV_38ALT_Carpark_Lot_1</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Carpark_Lot_1</t>
-  </si>
-  <si>
     <t>SOV 38ALT Carpark Lot 1 VA ILLEGAL PARKING</t>
   </si>
   <si>
@@ -145,9 +133,6 @@
     <t>SOV_38ALT_L1_Lift Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L1_Lift Lobby</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l1-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -157,9 +142,6 @@
     <t>SOV_38ALT_L4_Corridor_o/s_War_Room</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Corridor_o/s_War_Room</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-corridor-o-s-war-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -169,9 +151,6 @@
     <t>SOV_38ALT_L4_Interlock</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Interlock</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-interlock-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -181,9 +160,6 @@
     <t>SOV_38ALT_L5_Corridor</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_Corridor</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-corridor-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -196,9 +172,6 @@
     <t>SOV_38ALT_Side_Fencing</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Side_Fencing</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-intrusion -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -214,9 +187,6 @@
     <t>SOV_38ALT_Roof_Top</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Roof_Top</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-roof-top-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -226,9 +196,6 @@
     <t>SOV_38ALT_L2_Lift Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Lift Lobby</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -238,9 +205,6 @@
     <t>SOV_38ALT_L3_Lift_Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L3_Lift_Lobby</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l3-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -250,9 +214,6 @@
     <t>SOV_38ALT_L2_Main_Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Main_Lobby</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-main-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -262,9 +223,6 @@
     <t>SOV_38ALT_L2_Reception</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Reception</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-reception-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -274,9 +232,6 @@
     <t>SOV_38ALT_Main_Road</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Road</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-road-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -286,9 +241,6 @@
     <t>SOV_38ALT_L6_Lift Lobby</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L6_Lift Lobby</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l6-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -298,9 +250,6 @@
     <t>SOV_38ALT_L5_o/s_Cyber_Room</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_o/s_Cyber_Room</t>
-  </si>
-  <si>
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-o-s-cyber-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
@@ -310,9 +259,6 @@
     <t>SOV_38ALT_Main_Gate_Perimeter</t>
   </si>
   <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Gate_Perimeter</t>
-  </si>
-  <si>
     <t>SOV 38ALT Main Gate Perimiter VA INTRUSION</t>
   </si>
   <si>
@@ -362,6 +308,9 @@
   </si>
   <si>
     <t>SOV 38ALT L5 o/s Cyber Room VA LOITERING</t>
+  </si>
+  <si>
+    <t>https://soverus-hq-vg.somesolutions.xyz/stream.html?src=SOV_38ALT_Carpark_Lot_1&amp;token={{token}}</t>
   </si>
 </sst>
 </file>
@@ -452,7 +401,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,6 +417,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -869,9 +819,6 @@
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" s="3">
         <v>1</v>
       </c>
@@ -885,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -899,17 +846,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="3">
         <v>1</v>
       </c>
@@ -923,13 +868,13 @@
         <v>3</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,37 +882,35 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -975,37 +918,35 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1013,16 +954,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1037,13 +978,13 @@
         <v>4</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N6" s="6"/>
     </row>
@@ -1055,14 +996,12 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="3">
         <v>1</v>
       </c>
@@ -1076,13 +1015,13 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,14 +1032,12 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="3">
         <v>1</v>
       </c>
@@ -1114,13 +1051,13 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1131,14 +1068,12 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="3">
         <v>1</v>
       </c>
@@ -1152,13 +1087,13 @@
         <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1169,14 +1104,12 @@
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="3">
         <v>1</v>
       </c>
@@ -1190,13 +1123,13 @@
         <v>2</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1204,17 +1137,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="3">
         <v>1</v>
       </c>
@@ -1228,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1242,17 +1173,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="3">
         <v>1</v>
       </c>
@@ -1266,13 +1195,13 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1280,17 +1209,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="3">
         <v>1</v>
       </c>
@@ -1304,13 +1231,13 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1321,14 +1248,12 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="3">
         <v>1</v>
       </c>
@@ -1342,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1359,14 +1284,12 @@
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="3">
         <v>1</v>
       </c>
@@ -1380,13 +1303,13 @@
         <v>2</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1397,14 +1320,12 @@
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="3">
         <v>1</v>
       </c>
@@ -1418,13 +1339,13 @@
         <v>2</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1435,14 +1356,12 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="3">
         <v>1</v>
       </c>
@@ -1456,13 +1375,13 @@
         <v>2</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1473,14 +1392,12 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>80</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="3">
         <v>1</v>
       </c>
@@ -1494,13 +1411,13 @@
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1511,14 +1428,12 @@
         <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E19" s="4"/>
       <c r="F19" s="3">
         <v>1</v>
       </c>
@@ -1532,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1549,14 +1464,12 @@
         <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E20" s="4"/>
       <c r="F20" s="3">
         <v>1</v>
       </c>
@@ -1570,13 +1483,13 @@
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1587,14 +1500,12 @@
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E21" s="4"/>
       <c r="F21" s="3">
         <v>1</v>
       </c>
@@ -1608,13 +1519,13 @@
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1622,17 +1533,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="3">
         <v>1</v>
       </c>
@@ -1646,36 +1555,18 @@
         <v>1</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{B28935B8-16B4-4EE6-B2F6-2B7684B4D9D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ZAARR-DTE\taylor-imops-lite\packages\backend\src\scripts\soverus\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8144BD96-94ED-40C3-AA2F-EA77F4E7718A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB8F975-8749-4CE2-9D96-0409ABB35233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -271,18 +284,12 @@
     <t>SOV 38ALT L4 Corridor o/s War Room VA LOITERING</t>
   </si>
   <si>
-    <t>SOV 38ALT L4 Interlock VA  LOITERING</t>
-  </si>
-  <si>
     <t>SOV 38ALT L5 Corridor VA LOITERING</t>
   </si>
   <si>
     <t>SOV 38ALT Side Fencing VA INTRUSION</t>
   </si>
   <si>
-    <t>SOV 38ALT Side Fencing  VA SMOKING</t>
-  </si>
-  <si>
     <t>SOV 38ALT Side Fencing VA FIRE</t>
   </si>
   <si>
@@ -311,6 +318,21 @@
   </si>
   <si>
     <t>https://soverus-hq-vg.somesolutions.xyz/stream.html?src=SOV_38ALT_Carpark_Lot_1&amp;token={{token}}</t>
+  </si>
+  <si>
+    <t>Work? [Live,Snap, Play]</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L4 Interlock VA LOITERING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT Side Fencing VA SMOKING</t>
+  </si>
+  <si>
+    <t>if one by one okay</t>
+  </si>
+  <si>
+    <t>combine 15 + 16 playback would failed</t>
   </si>
 </sst>
 </file>
@@ -343,12 +365,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -358,8 +374,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,8 +393,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -396,28 +423,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -754,21 +809,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="21.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="34.140625" customWidth="1"/>
-    <col min="11" max="11" width="32.140625" customWidth="1"/>
-    <col min="12" max="12" width="121.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.453125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" customWidth="1"/>
+    <col min="10" max="10" width="34.1796875" customWidth="1"/>
+    <col min="11" max="11" width="32.1796875" customWidth="1"/>
+    <col min="12" max="12" width="121.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -805,9 +861,12 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="M1" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -837,12 +896,15 @@
       <c r="K2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="M2" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -873,12 +935,15 @@
       <c r="K3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="M3" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -909,12 +974,15 @@
       <c r="K4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="M4" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -948,9 +1016,12 @@
       <c r="L5" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="M5" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -962,8 +1033,8 @@
       <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>96</v>
+      <c r="E6" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -986,10 +1057,13 @@
       <c r="L6" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="M6" s="12">
+        <v>111</v>
+      </c>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1023,9 +1097,12 @@
       <c r="L7" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="M7" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1059,9 +1136,12 @@
       <c r="L8" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="M8" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1087,7 +1167,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>12</v>
@@ -1095,9 +1175,12 @@
       <c r="L9" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="M9" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1123,7 +1206,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>12</v>
@@ -1131,9 +1214,12 @@
       <c r="L10" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="M10" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1159,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>47</v>
@@ -1167,9 +1253,12 @@
       <c r="L11" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="M11" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1195,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>22</v>
@@ -1203,9 +1292,12 @@
       <c r="L12" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="M12" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1231,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>27</v>
@@ -1239,9 +1331,12 @@
       <c r="L13" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="M13" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1267,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>12</v>
@@ -1275,9 +1370,12 @@
       <c r="L14" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="M14" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1303,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>12</v>
@@ -1311,9 +1409,15 @@
       <c r="L15" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="M15" s="12">
+        <v>111</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1339,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>12</v>
@@ -1347,9 +1451,15 @@
       <c r="L16" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="M16" s="12">
+        <v>110</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1375,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>12</v>
@@ -1383,9 +1493,12 @@
       <c r="L17" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="M17" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1411,7 +1524,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>12</v>
@@ -1419,9 +1532,10 @@
       <c r="L18" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1447,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>12</v>
@@ -1455,9 +1569,10 @@
       <c r="L19" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1483,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>12</v>
@@ -1491,9 +1606,10 @@
       <c r="L20" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="14">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1519,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
@@ -1527,9 +1643,10 @@
       <c r="L21" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1563,6 +1680,7 @@
       <c r="L22" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="M22" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB8F975-8749-4CE2-9D96-0409ABB35233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2E97F7-5D17-4411-B122-880AC2A951D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -266,9 +266,6 @@
     <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-o-s-cyber-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
   </si>
   <si>
-    <t>SOV 38ALT Main Gate Perimiter</t>
-  </si>
-  <si>
     <t>SOV_38ALT_Main_Gate_Perimeter</t>
   </si>
   <si>
@@ -329,10 +326,7 @@
     <t>SOV 38ALT Side Fencing VA SMOKING</t>
   </si>
   <si>
-    <t>if one by one okay</t>
-  </si>
-  <si>
-    <t>combine 15 + 16 playback would failed</t>
+    <t>SOV 38ALT Main Gate Perimeter</t>
   </si>
 </sst>
 </file>
@@ -439,7 +433,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -466,10 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -809,22 +800,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="21.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.453125" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" customWidth="1"/>
-    <col min="9" max="9" width="12.7265625" customWidth="1"/>
-    <col min="10" max="10" width="34.1796875" customWidth="1"/>
-    <col min="11" max="11" width="32.1796875" customWidth="1"/>
-    <col min="12" max="12" width="121.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="34.140625" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" customWidth="1"/>
+    <col min="12" max="12" width="121.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,10 +853,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -903,7 +894,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -942,7 +933,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -981,7 +972,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1020,7 +1011,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1034,7 +1025,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1062,7 +1053,7 @@
       </c>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1089,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>12</v>
@@ -1101,7 +1092,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1128,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>12</v>
@@ -1140,7 +1131,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1167,7 +1158,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>12</v>
@@ -1179,7 +1170,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1206,7 +1197,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>12</v>
@@ -1218,7 +1209,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1245,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>47</v>
@@ -1257,7 +1248,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1284,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>22</v>
@@ -1296,7 +1287,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1323,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>27</v>
@@ -1335,7 +1326,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1362,7 +1353,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>12</v>
@@ -1374,7 +1365,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -1401,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>12</v>
@@ -1412,12 +1403,10 @@
       <c r="M15" s="12">
         <v>111</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16">
+      <c r="N15" s="14"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1443,7 +1432,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>12</v>
@@ -1452,14 +1441,12 @@
         <v>61</v>
       </c>
       <c r="M16" s="12">
-        <v>110</v>
-      </c>
-      <c r="N16" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="16">
+        <v>111</v>
+      </c>
+      <c r="N16" s="14"/>
+    </row>
+    <row r="17" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1485,7 +1472,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>12</v>
@@ -1494,10 +1481,10 @@
         <v>64</v>
       </c>
       <c r="M17" s="12">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -1524,7 +1511,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>12</v>
@@ -1532,10 +1519,12 @@
       <c r="L18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="14">
+      <c r="M18" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1561,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>12</v>
@@ -1569,10 +1558,12 @@
       <c r="L19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="14">
+      <c r="M19" s="12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1598,7 +1589,7 @@
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>12</v>
@@ -1606,10 +1597,12 @@
       <c r="L20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="M20" s="12"/>
-    </row>
-    <row r="21" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="14">
+      <c r="M20" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1635,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>12</v>
@@ -1643,20 +1636,22 @@
       <c r="L21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="M21" s="12"/>
-    </row>
-    <row r="22" spans="1:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="14">
+      <c r="M21" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="3">
@@ -1672,15 +1667,17 @@
         <v>1</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="M22" s="12"/>
+        <v>79</v>
+      </c>
+      <c r="M22" s="12">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2E97F7-5D17-4411-B122-880AC2A951D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469F0A64-911B-4045-9A32-5B2AF2B2CB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -374,7 +374,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,12 +384,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -461,9 +455,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1524,7 +1515,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1559,7 +1550,7 @@
         <v>70</v>
       </c>
       <c r="M19" s="12">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
